--- a/resources/RAM205_kit_BOM.xlsx
+++ b/resources/RAM205_kit_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://k2controls-my.sharepoint.com/personal/keith_k2controls_net/Documents/NMC/courses/piRover02/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{54365E58-501F-40F3-8C88-41B5A6541E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6176A384-C7D5-435C-A4D3-39684F07136D}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{54365E58-501F-40F3-8C88-41B5A6541E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B707D375-E7B3-45EE-8F76-EF3EEE831DA1}"/>
   <bookViews>
-    <workbookView xWindow="3737" yWindow="3737" windowWidth="18514" windowHeight="10714" xr2:uid="{C5A32510-B305-4331-9E1B-79CCF2794904}"/>
+    <workbookView xWindow="22370" yWindow="19820" windowWidth="18920" windowHeight="16850" xr2:uid="{C5A32510-B305-4331-9E1B-79CCF2794904}"/>
   </bookViews>
   <sheets>
     <sheet name="RAM205Kit" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
   <si>
     <t>Student Kit</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>122/13/2023</t>
-  </si>
-  <si>
     <t>Jumper wires Male to Male 10cm (10x - 10 colors)</t>
   </si>
   <si>
@@ -218,10 +215,16 @@
     <t>LED assembly screw (included in Trailer LED package?)</t>
   </si>
   <si>
-    <t>https://www.amazon.com/dp/B00H1WXXFY/?coliid=I37G8OSOYUHMC6&amp;colid=14M9USMIS5DRN&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it</t>
-  </si>
-  <si>
     <t>Storage container</t>
+  </si>
+  <si>
+    <t>AA Battery</t>
+  </si>
+  <si>
+    <t>Amazon.com: Meal Prep Containers, [34oz 50Pack] Food Prep Containers with Lids, Disposable To Go Containers, Plastic Food Storage Containers with Lids, BPA Free, Stackable, Microwave/Dishwasher/Freezer Safe: Home &amp; Kitchen</t>
+  </si>
+  <si>
+    <t>Amazon.com: Voniko - Premium Grade AA Batteries - (24 Pack) - Alkaline Double A Battery - Ultra Long-Lasting, Leakproof 1.5v Batteries - 10-Year Shelf Life : Health &amp; Household</t>
   </si>
 </sst>
 </file>
@@ -602,10 +605,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -908,21 +907,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:T32"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="15.9"/>
+  <dimension ref="A1:T33"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="7.3828125" style="2" customWidth="1"/>
-    <col min="2" max="5" width="2.3828125" style="3" customWidth="1"/>
-    <col min="6" max="10" width="2.3828125" style="3" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="10.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="43.3828125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.3828125" style="2" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="8.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.84375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" style="2" customWidth="1"/>
+    <col min="2" max="5" width="2.36328125" style="3" customWidth="1"/>
+    <col min="6" max="10" width="2.36328125" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="43.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.36328125" style="2" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="8.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="9.84375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="30.3046875" style="4" customWidth="1"/>
-    <col min="20" max="16384" width="9.15234375" style="4"/>
+    <col min="17" max="18" width="9.81640625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="30.26953125" style="4" customWidth="1"/>
+    <col min="20" max="16384" width="9.1796875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="11.25" customHeight="1" thickBot="1">
@@ -999,7 +998,7 @@
       <c r="I4" s="37"/>
       <c r="J4" s="37"/>
       <c r="K4" s="23">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="L4" s="23"/>
       <c r="M4" s="31"/>
@@ -1024,8 +1023,8 @@
       <c r="H5" s="40"/>
       <c r="I5" s="40"/>
       <c r="J5" s="40"/>
-      <c r="K5" s="24" t="s">
-        <v>54</v>
+      <c r="K5" s="24">
+        <v>45308</v>
       </c>
       <c r="L5" s="24"/>
       <c r="M5" s="32"/>
@@ -1038,7 +1037,7 @@
       <c r="T5" s="5"/>
     </row>
     <row r="6" spans="1:20" ht="9" customHeight="1" thickBot="1"/>
-    <row r="7" spans="1:20" s="12" customFormat="1" ht="29.15">
+    <row r="7" spans="1:20" s="12" customFormat="1" ht="29">
       <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
@@ -1423,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="14" t="str">
-        <f t="shared" ref="B14:E29" si="3">IF($A14=B$7,"*"," ")</f>
+        <f t="shared" ref="B14:E30" si="3">IF($A14=B$7,"*"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="C14" s="14" t="str">
@@ -1547,7 +1546,7 @@
       <c r="J16" s="14"/>
       <c r="K16" s="15"/>
       <c r="L16" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M16" s="17"/>
       <c r="N16" s="17">
@@ -1598,7 +1597,7 @@
       <c r="J17" s="14"/>
       <c r="K17" s="15"/>
       <c r="L17" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M17" s="17"/>
       <c r="N17" s="17">
@@ -1721,7 +1720,7 @@
         <v>0.6</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2053,7 +2052,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="15"/>
       <c r="L26" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M26" s="17"/>
       <c r="N26" s="17">
@@ -2204,11 +2203,11 @@
       <c r="J29" s="14"/>
       <c r="K29" s="15"/>
       <c r="L29" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M29" s="17"/>
       <c r="N29" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="17" t="s">
         <v>9</v>
@@ -2217,57 +2216,108 @@
         <v>10</v>
       </c>
       <c r="Q29" s="18">
-        <f>13.19/6</f>
-        <v>2.1983333333333333</v>
+        <f>9.5/24</f>
+        <v>0.39583333333333331</v>
       </c>
       <c r="R29" s="18">
         <f>N29*Q29</f>
-        <v>2.1983333333333333</v>
-      </c>
-      <c r="S29" s="25" t="s">
-        <v>59</v>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:19">
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="A30" s="13">
+        <v>1</v>
+      </c>
+      <c r="B30" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C30" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v>*</v>
+      </c>
+      <c r="D30" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="E30" s="14" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17">
+        <v>1</v>
+      </c>
+      <c r="O30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="P30" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="18">
+        <f>17/50</f>
+        <v>0.34</v>
+      </c>
+      <c r="R30" s="18">
+        <f>N30*Q30</f>
+        <v>0.34</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="2" t="s">
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Q31" s="12" t="s">
+      <c r="Q32" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="R31" s="20">
-        <f>SUM(R8:R29)</f>
-        <v>25.286300000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="21"/>
+      <c r="R32" s="20">
+        <f>SUM(R8:R30)</f>
+        <v>24.219633333333334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2297,9 +2347,11 @@
     <hyperlink ref="S13" r:id="rId14" xr:uid="{36A93EAF-5614-457E-BBA1-2F9A671CE385}"/>
     <hyperlink ref="S19" r:id="rId15" display="https://www.amazon.com/dp/B07WF76VHT/?coliid=I3L6DHCMWM1S6W&amp;colid=14M9USMIS5DRN&amp;ref_=list_c_wl_lv_ov_lig_dp_it&amp;th=1" xr:uid="{1876FCB9-AC87-4747-BFF3-475AC6B19E8A}"/>
     <hyperlink ref="S28" r:id="rId16" xr:uid="{D6250C10-F82A-423B-A7AF-C64FDD7B81C9}"/>
+    <hyperlink ref="S30" r:id="rId17" display="https://www.amazon.com/dp/B0BXW86JZQ/?coliid=I12DMLQWWJ9K4J&amp;colid=14M9USMIS5DRN&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it" xr:uid="{586775DA-0102-4B34-B6F8-5E9F5E35E5FA}"/>
+    <hyperlink ref="S29" r:id="rId18" display="https://www.amazon.com/dp/B07RX92Y43/?coliid=I2P9668VT0RNU1&amp;colid=14M9USMIS5DRN&amp;psc=1&amp;ref_=list_c_wl_lv_ov_lig_dp_it" xr:uid="{189EA1D7-C9AF-47FF-AFBD-9173A4AAF037}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId17"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId19"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;D&amp;CThis BOM template is available compliments of Arena Solutions - www.arenasolutions.com&amp;Rpage&amp;P of &amp;N</oddFooter>
   </headerFooter>
